--- a/data/trans_dic/P56$pareja-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$pareja-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,65; 56,0</t>
+          <t>28,03; 55,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,86; 54,67</t>
+          <t>27,9; 54,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,48; 60,82</t>
+          <t>35,46; 60,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 42,21</t>
+          <t>24,15; 41,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 18,57</t>
+          <t>4,76; 18,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,79; 20,8</t>
+          <t>10,24; 20,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 18,71</t>
+          <t>6,52; 18,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,63; 17,65</t>
+          <t>11,03; 18,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,93; 29,58</t>
+          <t>15,0; 29,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,41; 27,66</t>
+          <t>16,03; 27,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,15; 27,86</t>
+          <t>16,3; 28,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,34; 22,27</t>
+          <t>15,26; 22,06</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,22; 88,8</t>
+          <t>31,99; 88,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 64,79</t>
+          <t>9,89; 66,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,09; 52,41</t>
+          <t>22,97; 51,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,9</t>
+          <t>0,0; 61,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,79</t>
+          <t>0,0; 33,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,61; 56,5</t>
+          <t>15,01; 56,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,57; 29,56</t>
+          <t>11,85; 28,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 56,87</t>
+          <t>7,18; 52,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,22; 57,89</t>
+          <t>14,24; 54,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,9; 51,28</t>
+          <t>18,18; 53,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,9; 34,37</t>
+          <t>18,77; 35,75</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31,2; 91,5</t>
+          <t>28,75; 90,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,84</t>
+          <t>0,0; 40,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,86</t>
+          <t>0,0; 81,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,32</t>
+          <t>0,0; 80,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,12; 61,71</t>
+          <t>19,22; 59,02</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,42; 56,12</t>
+          <t>30,1; 57,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,3; 55,11</t>
+          <t>30,14; 55,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36,82; 59,55</t>
+          <t>35,47; 57,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,2; 43,61</t>
+          <t>28,8; 43,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 19,31</t>
+          <t>5,82; 19,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,02; 20,16</t>
+          <t>10,08; 20,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 20,57</t>
+          <t>8,57; 20,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,85; 18,58</t>
+          <t>11,84; 18,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,67; 28,44</t>
+          <t>15,68; 28,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,63; 28,83</t>
+          <t>17,81; 28,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,6; 30,21</t>
+          <t>18,37; 29,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 24,54</t>
+          <t>17,73; 24,16</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda su pareja cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12646; 24714</t>
+          <t>12369; 24586</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19055; 37389</t>
+          <t>19084; 37534</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20681; 34479</t>
+          <t>20101; 34317</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16487; 28665</t>
+          <t>16396; 27899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4166; 15494</t>
+          <t>3967; 15378</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18201; 38678</t>
+          <t>19045; 38223</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8800; 26709</t>
+          <t>9308; 26477</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21324; 35403</t>
+          <t>22116; 36093</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19045; 37729</t>
+          <t>19135; 37092</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41733; 70339</t>
+          <t>40782; 69798</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32201; 55553</t>
+          <t>32512; 56208</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41183; 59794</t>
+          <t>40981; 59230</t>
         </is>
       </c>
     </row>
@@ -1717,57 +1717,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2941; 8104</t>
+          <t>2919; 8109</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1045; 7244</t>
+          <t>1106; 7466</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6257; 14204</t>
+          <t>6227; 13976</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4190</t>
+          <t>0; 4171</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3975</t>
+          <t>0; 3992</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3961; 14342</t>
+          <t>3810; 14407</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4868; 12435</t>
+          <t>4985; 12191</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>753; 6207</t>
+          <t>783; 5771</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2970; 12093</t>
+          <t>2975; 11473</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6545; 18749</t>
+          <t>6649; 19709</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13077; 23774</t>
+          <t>12981; 24732</t>
         </is>
       </c>
     </row>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 761</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2021; 5926</t>
+          <t>1862; 5845</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1630</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2771</t>
+          <t>0; 2627</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4373</t>
+          <t>0; 4387</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6185</t>
+          <t>0; 6349</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2475; 7989</t>
+          <t>2489; 7640</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13721; 27095</t>
+          <t>14530; 27529</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23790; 43266</t>
+          <t>23659; 43177</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26543; 42937</t>
+          <t>25572; 41326</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28621; 44258</t>
+          <t>29228; 43956</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5814; 18067</t>
+          <t>5442; 17941</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20257; 40750</t>
+          <t>20383; 40983</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14854; 35333</t>
+          <t>14730; 35472</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29524; 46290</t>
+          <t>29485; 46268</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22230; 40330</t>
+          <t>22241; 41080</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49483; 80918</t>
+          <t>49969; 78775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45362; 73683</t>
+          <t>44807; 72443</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62805; 86049</t>
+          <t>62154; 84692</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$pareja-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$pareja-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,03; 55,71</t>
+          <t>28,36; 57,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,9; 54,88</t>
+          <t>27,62; 54,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,46; 60,54</t>
+          <t>35,81; 60,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,15; 41,09</t>
+          <t>24,95; 41,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 18,44</t>
+          <t>5,11; 18,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 20,56</t>
+          <t>9,98; 21,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,52; 18,55</t>
+          <t>6,37; 18,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,03; 18,0</t>
+          <t>10,39; 17,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,0; 29,08</t>
+          <t>14,51; 29,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,03; 27,44</t>
+          <t>16,24; 28,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,3; 28,19</t>
+          <t>16,59; 28,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,26; 22,06</t>
+          <t>14,96; 22,34</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,99; 88,86</t>
+          <t>31,95; 89,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 66,78</t>
+          <t>10,15; 67,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22,97; 51,57</t>
+          <t>23,45; 53,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,61</t>
+          <t>0,0; 59,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,94</t>
+          <t>0,0; 34,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,01; 56,76</t>
+          <t>14,2; 55,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 28,98</t>
+          <t>12,08; 29,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 52,88</t>
+          <t>6,72; 53,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,24; 54,92</t>
+          <t>14,07; 58,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 53,9</t>
+          <t>19,52; 54,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,77; 35,75</t>
+          <t>19,65; 34,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,75; 90,25</t>
+          <t>36,99; 92,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 76,81</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 46,64</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 40,61</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,1</t>
+          <t>0,0; 81,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,39</t>
+          <t>0,0; 80,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,22; 59,02</t>
+          <t>19,35; 61,8</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,1; 57,02</t>
+          <t>27,88; 54,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,14; 55,0</t>
+          <t>30,44; 55,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,47; 57,32</t>
+          <t>37,16; 59,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,8; 43,31</t>
+          <t>28,79; 43,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 19,18</t>
+          <t>6,24; 20,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 20,28</t>
+          <t>10,62; 20,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,57; 20,65</t>
+          <t>8,91; 20,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,84; 18,57</t>
+          <t>12,02; 18,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,68; 28,97</t>
+          <t>16,13; 29,62</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,81; 28,07</t>
+          <t>17,68; 28,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,37; 29,7</t>
+          <t>18,48; 29,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,73; 24,16</t>
+          <t>18,01; 24,3</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21905</t>
+          <t>23490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28113</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50017</t>
+          <t>53844</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12369; 24586</t>
+          <t>12517; 25201</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19084; 37534</t>
+          <t>18887; 37098</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20101; 34317</t>
+          <t>20301; 34476</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16396; 27899</t>
+          <t>18023; 30302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3967; 15378</t>
+          <t>4260; 15065</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19045; 38223</t>
+          <t>18551; 39340</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9308; 26477</t>
+          <t>9086; 26558</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22116; 36093</t>
+          <t>22558; 37925</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19135; 37092</t>
+          <t>18511; 37805</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40782; 69798</t>
+          <t>41297; 71774</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32512; 56208</t>
+          <t>33081; 56067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40981; 59230</t>
+          <t>43301; 64642</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>20407</t>
         </is>
       </c>
     </row>
@@ -1717,57 +1717,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2919; 8109</t>
+          <t>2916; 8136</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1106; 7466</t>
+          <t>1135; 7551</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6227; 13976</t>
+          <t>6706; 15324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4171</t>
+          <t>0; 4053</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3992</t>
+          <t>0; 4065</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3810; 14407</t>
+          <t>3605; 14170</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4985; 12191</t>
+          <t>5807; 14290</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>783; 5771</t>
+          <t>733; 5790</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2975; 11473</t>
+          <t>2940; 12166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6649; 19709</t>
+          <t>7136; 19851</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12981; 24732</t>
+          <t>15059; 26665</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>6244</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1862; 5845</t>
+          <t>2644; 6584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4423</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2627</t>
+          <t>0; 3809</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4387</t>
+          <t>0; 4419</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 6349</t>
+          <t>0; 6327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2489; 7640</t>
+          <t>2963; 9465</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>39156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36915</t>
+          <t>41340</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73058</t>
+          <t>80496</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14530; 27529</t>
+          <t>13462; 26214</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23659; 43177</t>
+          <t>23900; 43723</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25572; 41326</t>
+          <t>26789; 43080</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>29228; 43956</t>
+          <t>31085; 47317</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5442; 17941</t>
+          <t>5841; 19438</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20383; 40983</t>
+          <t>21471; 42143</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14730; 35472</t>
+          <t>15306; 35917</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29485; 46268</t>
+          <t>32849; 51163</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22241; 41080</t>
+          <t>22875; 42002</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49969; 78775</t>
+          <t>49615; 80663</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44807; 72443</t>
+          <t>45064; 73099</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62154; 84692</t>
+          <t>68689; 92688</t>
         </is>
       </c>
     </row>
